--- a/artfynd/A 38453-2026 artfynd.xlsx
+++ b/artfynd/A 38453-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1510,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129189739</v>
+        <v>128364532</v>
       </c>
       <c r="B10" t="n">
-        <v>92208</v>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,37 +1521,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tjiärmadahkka , Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607736</v>
+        <v>607627</v>
       </c>
       <c r="R10" t="n">
-        <v>7326390</v>
+        <v>7326556</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,12 +1575,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,34 +1599,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129189739</t>
+          <t>https://artportalen.se/Sighting/128364532</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128364532</v>
+        <v>127079568</v>
       </c>
       <c r="B11" t="n">
-        <v>79406</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1627,34 +1633,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607627</v>
+        <v>607570</v>
       </c>
       <c r="R11" t="n">
-        <v>7326556</v>
+        <v>7326549</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,22 +1687,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:07</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,51 +1718,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128364532</t>
+          <t>https://artportalen.se/Sighting/127079568</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127079568</v>
+        <v>127078849</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Långholmen, Långholmen, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607570</v>
+        <v>607506</v>
       </c>
       <c r="R12" t="n">
-        <v>7326549</v>
+        <v>7326767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,51 +1820,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127079568</t>
+          <t>https://artportalen.se/Sighting/127078849</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127078849</v>
+        <v>127078644</v>
       </c>
       <c r="B13" t="n">
-        <v>92083</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långholmen, Långholmen, Pi lm</t>
+          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607506</v>
+        <v>607586</v>
       </c>
       <c r="R13" t="n">
-        <v>7326767</v>
+        <v>7326861</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,13 +1922,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127078849</t>
+          <t>https://artportalen.se/Sighting/127078644</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127078644</v>
+        <v>127078742</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -1967,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607586</v>
+        <v>607552</v>
       </c>
       <c r="R14" t="n">
-        <v>7326861</v>
+        <v>7326830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,51 +2024,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127078644</t>
+          <t>https://artportalen.se/Sighting/127078742</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127078742</v>
+        <v>127076783</v>
       </c>
       <c r="B15" t="n">
-        <v>93197</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Båsjargŋa, Båsjargŋa, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607552</v>
+        <v>607730</v>
       </c>
       <c r="R15" t="n">
-        <v>7326830</v>
+        <v>7326604</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,38 +2126,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127078742</t>
+          <t>https://artportalen.se/Sighting/127076783</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127076783</v>
+        <v>127079200</v>
       </c>
       <c r="B16" t="n">
-        <v>91872</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2171,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607730</v>
+        <v>607506</v>
       </c>
       <c r="R16" t="n">
-        <v>7326604</v>
+        <v>7326696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,38 +2228,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127076783</t>
+          <t>https://artportalen.se/Sighting/127079200</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127079200</v>
+        <v>127074651</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2273,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607506</v>
+        <v>607532</v>
       </c>
       <c r="R17" t="n">
-        <v>7326696</v>
+        <v>7326271</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,13 +2330,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127079200</t>
+          <t>https://artportalen.se/Sighting/127074651</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127074651</v>
+        <v>127074941</v>
       </c>
       <c r="B18" t="n">
         <v>78730</v>
@@ -2375,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607532</v>
+        <v>607611</v>
       </c>
       <c r="R18" t="n">
-        <v>7326271</v>
+        <v>7326390</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,13 +2432,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127074651</t>
+          <t>https://artportalen.se/Sighting/127074941</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127074941</v>
+        <v>127078526</v>
       </c>
       <c r="B19" t="n">
         <v>78730</v>
@@ -2477,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607611</v>
+        <v>607630</v>
       </c>
       <c r="R19" t="n">
-        <v>7326390</v>
+        <v>7326801</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2538,13 +2534,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127074941</t>
+          <t>https://artportalen.se/Sighting/127078526</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127078526</v>
+        <v>128364543</v>
       </c>
       <c r="B20" t="n">
         <v>78730</v>
@@ -2575,14 +2571,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607630</v>
+        <v>607627</v>
       </c>
       <c r="R20" t="n">
-        <v>7326801</v>
+        <v>7326556</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2609,12 +2605,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,13 +2646,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127078526</t>
+          <t>https://artportalen.se/Sighting/128364543</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128364543</v>
+        <v>128364544</v>
       </c>
       <c r="B21" t="n">
         <v>78730</v>
@@ -2681,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607627</v>
+        <v>607746</v>
       </c>
       <c r="R21" t="n">
-        <v>7326556</v>
+        <v>7326692</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2726,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2752,16 +2758,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128364543</t>
+          <t>https://artportalen.se/Sighting/128364544</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128364544</v>
+        <v>127074704</v>
       </c>
       <c r="B22" t="n">
-        <v>78730</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2769,34 +2775,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607746</v>
+        <v>607555</v>
       </c>
       <c r="R22" t="n">
-        <v>7326692</v>
+        <v>7326287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,22 +2829,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:55</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:55</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,16 +2860,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128364544</t>
+          <t>https://artportalen.se/Sighting/127074704</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127074704</v>
+        <v>127074949</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2881,21 +2877,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2905,10 +2901,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607555</v>
+        <v>607611</v>
       </c>
       <c r="R23" t="n">
-        <v>7326287</v>
+        <v>7326390</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,13 +2962,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127074704</t>
+          <t>https://artportalen.se/Sighting/127074949</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127074949</v>
+        <v>127075134</v>
       </c>
       <c r="B24" t="n">
         <v>79946</v>
@@ -3007,10 +3003,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607611</v>
+        <v>607634</v>
       </c>
       <c r="R24" t="n">
-        <v>7326390</v>
+        <v>7326481</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3068,13 +3064,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127074949</t>
+          <t>https://artportalen.se/Sighting/127075134</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127075134</v>
+        <v>127076330</v>
       </c>
       <c r="B25" t="n">
         <v>79946</v>
@@ -3109,10 +3105,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607634</v>
+        <v>607710</v>
       </c>
       <c r="R25" t="n">
-        <v>7326481</v>
+        <v>7326472</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3170,13 +3166,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127075134</t>
+          <t>https://artportalen.se/Sighting/127076330</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127076330</v>
+        <v>127076452</v>
       </c>
       <c r="B26" t="n">
         <v>79946</v>
@@ -3211,10 +3207,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607710</v>
+        <v>607721</v>
       </c>
       <c r="R26" t="n">
-        <v>7326472</v>
+        <v>7326477</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,13 +3268,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127076330</t>
+          <t>https://artportalen.se/Sighting/127076452</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127076452</v>
+        <v>127076668</v>
       </c>
       <c r="B27" t="n">
         <v>79946</v>
@@ -3313,10 +3309,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607721</v>
+        <v>607787</v>
       </c>
       <c r="R27" t="n">
-        <v>7326477</v>
+        <v>7326543</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,13 +3370,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127076452</t>
+          <t>https://artportalen.se/Sighting/127076668</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127076668</v>
+        <v>127077017</v>
       </c>
       <c r="B28" t="n">
         <v>79946</v>
@@ -3415,10 +3411,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607787</v>
+        <v>607714</v>
       </c>
       <c r="R28" t="n">
-        <v>7326543</v>
+        <v>7326595</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,13 +3472,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127076668</t>
+          <t>https://artportalen.se/Sighting/127077017</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127077017</v>
+        <v>127079261</v>
       </c>
       <c r="B29" t="n">
         <v>79946</v>
@@ -3517,10 +3513,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607714</v>
+        <v>607534</v>
       </c>
       <c r="R29" t="n">
-        <v>7326595</v>
+        <v>7326663</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3578,13 +3574,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127077017</t>
+          <t>https://artportalen.se/Sighting/127079261</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127079261</v>
+        <v>128364512</v>
       </c>
       <c r="B30" t="n">
         <v>79946</v>
@@ -3615,14 +3611,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607534</v>
+        <v>607775</v>
       </c>
       <c r="R30" t="n">
-        <v>7326663</v>
+        <v>7326678</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3649,12 +3645,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3680,51 +3686,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127079261</t>
+          <t>https://artportalen.se/Sighting/128364512</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128364512</v>
+        <v>127074519</v>
       </c>
       <c r="B31" t="n">
-        <v>79946</v>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Korsträsk, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607775</v>
+        <v>607517</v>
       </c>
       <c r="R31" t="n">
-        <v>7326678</v>
+        <v>7326285</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3751,22 +3757,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:57</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:57</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3792,54 +3788,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128364512</t>
+          <t>https://artportalen.se/Sighting/127074519</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129188991</v>
+        <v>127076482</v>
       </c>
       <c r="B32" t="n">
-        <v>80336</v>
+        <v>78334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tjiärmadahkka , Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607815</v>
+        <v>607764</v>
       </c>
       <c r="R32" t="n">
-        <v>7326460</v>
+        <v>7326485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3866,12 +3859,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3880,61 +3873,61 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129188991</t>
+          <t>https://artportalen.se/Sighting/127076482</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129188988</v>
+        <v>129211232</v>
       </c>
       <c r="B33" t="n">
-        <v>80461</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3942,10 +3935,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607815</v>
+        <v>607765</v>
       </c>
       <c r="R33" t="n">
-        <v>7326460</v>
+        <v>7326469</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3972,12 +3965,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3986,7 +3994,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4004,16 +4011,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129188988</t>
+          <t>https://artportalen.se/Sighting/129211232</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127074519</v>
+        <v>129188674</v>
       </c>
       <c r="B34" t="n">
-        <v>80468</v>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4021,37 +4028,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Tjiärmadahkka , Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>607517</v>
+        <v>607648</v>
       </c>
       <c r="R34" t="n">
-        <v>7326285</v>
+        <v>7326543</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4075,12 +4090,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4095,27 +4110,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127074519</t>
+          <t>https://artportalen.se/Sighting/129188674</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127076482</v>
+        <v>127075079</v>
       </c>
       <c r="B35" t="n">
-        <v>78334</v>
+        <v>58114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4123,34 +4138,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>607764</v>
+        <v>607678</v>
       </c>
       <c r="R35" t="n">
-        <v>7326485</v>
+        <v>7326420</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4208,16 +4232,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127076482</t>
+          <t>https://artportalen.se/Sighting/127075079</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129211232</v>
+        <v>127078104</v>
       </c>
       <c r="B36" t="n">
-        <v>57953</v>
+        <v>58057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4225,16 +4249,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4243,20 +4267,21 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tjiärmadahkka , Pi lm</t>
+          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>607765</v>
+        <v>607755</v>
       </c>
       <c r="R36" t="n">
-        <v>7326469</v>
+        <v>7326703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4283,27 +4308,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4318,27 +4328,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129211232</t>
+          <t>https://artportalen.se/Sighting/127078104</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129188674</v>
+        <v>127079093</v>
       </c>
       <c r="B37" t="n">
-        <v>57141</v>
+        <v>106229</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,45 +4356,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tjiärmadahkka , Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>607648</v>
+        <v>607489</v>
       </c>
       <c r="R37" t="n">
-        <v>7326543</v>
+        <v>7326681</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4408,12 +4410,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4428,27 +4430,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129188674</t>
+          <t>https://artportalen.se/Sighting/127079093</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127075079</v>
+        <v>127074716</v>
       </c>
       <c r="B38" t="n">
-        <v>58114</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4456,43 +4458,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>607678</v>
+        <v>607555</v>
       </c>
       <c r="R38" t="n">
-        <v>7326420</v>
+        <v>7326287</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4550,16 +4543,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127075079</t>
+          <t>https://artportalen.se/Sighting/127074716</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127078104</v>
+        <v>127078504</v>
       </c>
       <c r="B39" t="n">
-        <v>58057</v>
+        <v>79917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4567,39 +4560,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Korsträsk SO Båtsjaur, Korsträsk SO Båtsjaur, Pi lm</t>
+          <t>Korsträsk, Korsträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>607755</v>
+        <v>607646</v>
       </c>
       <c r="R39" t="n">
-        <v>7326703</v>
+        <v>7326785</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4656,312 +4644,6 @@
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/127078104</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>127079093</v>
-      </c>
-      <c r="B40" t="n">
-        <v>106229</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>607489</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7326681</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/127079093</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>127074716</v>
-      </c>
-      <c r="B41" t="n">
-        <v>79085</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>607555</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7326287</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/127074716</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>127078504</v>
-      </c>
-      <c r="B42" t="n">
-        <v>79917</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Korsträsk, Korsträsk, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>607646</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7326785</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127078504</t>
         </is>
@@ -5007,9 +4689,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
